--- a/ResourcesBD/ProductExclusionFile1.xlsx
+++ b/ResourcesBD/ProductExclusionFile1.xlsx
@@ -14,7 +14,7 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
@@ -42,13 +42,13 @@
     <t>62732109</t>
   </si>
   <si>
-    <t xml:space="preserve">DIST </t>
-  </si>
-  <si>
     <t>15437620</t>
   </si>
   <si>
     <t>C14835</t>
+  </si>
+  <si>
+    <t>DIST</t>
   </si>
 </sst>
 </file>
@@ -399,13 +399,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>8</v>
-      </c>
-      <c r="D2" t="s">
-        <v>9</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>6</v>
